--- a/attendance_sheets/semester_register.xlsx
+++ b/attendance_sheets/semester_register.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 05-02-2026 07:18:27</t>
+          <t>Generated: 09-02-2026 09:23:58</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>04/02</t>
+          <t>08/02</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>05/02</t>
+          <t>09/02</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Jikmet Lama</t>
+          <t>Takap Lama</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -548,9 +548,9 @@
           <t>P</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chhakit Lama</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Jikmet lama</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -584,46 +584,68 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>Chhakit Lama</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>Sangat Maharjan</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>

--- a/attendance_sheets/semester_register.xlsx
+++ b/attendance_sheets/semester_register.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,10 +42,6 @@
     <font>
       <b val="1"/>
       <color rgb="00006100"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -101,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,10 +112,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,13 +480,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -506,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 09-02-2026 09:23:58</t>
+          <t>Generated: 11-02-2026 20:44:37</t>
         </is>
       </c>
     </row>
@@ -523,54 +515,39 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>08/02</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>09/02</t>
+          <t>11/02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Takap Lama</t>
+          <t>Alok Kumar Jha</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>P</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jikmet lama</t>
+          <t>Anurodh kharel</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -579,73 +556,165 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chhakit Lama</t>
+          <t>Avash</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>P</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>Bibek Kumar Jha</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Dikhant Joshi</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Dinesh Gurung</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Jikmet Wangchuk Lama</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Paras Pun</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>Sangat Maharjan</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>subodh upreti</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -653,7 +722,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
